--- a/script2/input/horus.xlsx
+++ b/script2/input/horus.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t xml:space="preserve">EAN</t>
   </si>
@@ -40,6 +40,18 @@
     <t xml:space="preserve">BaByliss 5914PE Hair Dryer</t>
   </si>
   <si>
+    <t xml:space="preserve">4242005183135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch BBHF214R Cordless Vacuum Cleaner Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4242002777450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch MFQ40303 Mixer</t>
+  </si>
+  <si>
     <t xml:space="preserve">4210201238591</t>
   </si>
   <si>
@@ -58,6 +70,12 @@
     <t xml:space="preserve">DeLonghi DLSC500 EcoDecalk Descaler 500 ml</t>
   </si>
   <si>
+    <t xml:space="preserve">8004399025370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeLonghi ECAM220.22.GB Magnifica Start Freestanding Coffee Machine</t>
+  </si>
+  <si>
     <t xml:space="preserve">8004399028371</t>
   </si>
   <si>
@@ -70,18 +88,6 @@
     <t xml:space="preserve">DeLonghi EN127.BL Freestanding Coffee Machine</t>
   </si>
   <si>
-    <t xml:space="preserve">6977728940212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dreame MOVA ATB15A-BK Electric Toothbrush</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6977728940205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dreame MOVA ATB15A-SL Electric Toothbrush</t>
-  </si>
-  <si>
     <t xml:space="preserve">6977328065452</t>
   </si>
   <si>
@@ -106,12 +112,6 @@
     <t xml:space="preserve">Dyson 598757-01 Airwrap Co-anda2x Hair Styler</t>
   </si>
   <si>
-    <t xml:space="preserve">8003753166889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">illy 22984 Milk Frother</t>
-  </si>
-  <si>
     <t xml:space="preserve">7610917155057</t>
   </si>
   <si>
@@ -124,6 +124,12 @@
     <t xml:space="preserve">Kitchenaid 5KEK1701EAC Electric Kettle</t>
   </si>
   <si>
+    <t xml:space="preserve">5413184905521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchenaid 5KEK1701EBK Electric Kettle</t>
+  </si>
+  <si>
     <t xml:space="preserve">5413184907952</t>
   </si>
   <si>
@@ -136,6 +142,12 @@
     <t xml:space="preserve">Kitchenaid 5KEK1701EPL Electric Kettle</t>
   </si>
   <si>
+    <t xml:space="preserve">5413184907914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchenaid 5KEK1701ESX Electric Kettle</t>
+  </si>
+  <si>
     <t xml:space="preserve">5413184124007</t>
   </si>
   <si>
@@ -160,6 +172,12 @@
     <t xml:space="preserve">Krups EA873810 Freestanding Coffee Machine Intuition Preference</t>
   </si>
   <si>
+    <t xml:space="preserve">4006508212958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melitta Molino 1019-01 Coffee Grinder</t>
+  </si>
+  <si>
     <t xml:space="preserve">4002516794202</t>
   </si>
   <si>
@@ -238,6 +256,12 @@
     <t xml:space="preserve">Philips DST2010/90 Iron</t>
   </si>
   <si>
+    <t xml:space="preserve">8710103970828, 8710103970842, 8720389013720, 8720389013737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philips STH3000/20 Clothes Steamer</t>
+  </si>
+  <si>
     <t xml:space="preserve">8720389035944</t>
   </si>
   <si>
@@ -248,6 +272,24 @@
   </si>
   <si>
     <t xml:space="preserve">Remington AS8930E51 Hair Straightener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5038061174731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remington CI8930 Hair Curler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4008496975846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remington S6700 Hair Straightener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8017709290672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smeg TSF01WHMEU Toaster 2 slice Matt White</t>
   </si>
   <si>
     <t xml:space="preserve">3121040085189</t>
@@ -265,7 +307,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="[$€-409]#,##0.00;\-[$€-409]#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,10 +331,17 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -339,33 +388,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -560,12 +605,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="75.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="76.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="0" width="11.53"/>
   </cols>
@@ -596,11 +641,11 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>26</v>
@@ -610,175 +655,175 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>17.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>374</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>415</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2</v>
+        <v>374</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>17</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>17</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>660</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>310</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>475</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>40</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="2" t="n">
@@ -792,7 +837,7 @@
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="2" t="n">
@@ -806,307 +851,405 @@
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>45</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>180</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>350</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>123</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>260</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>410</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>59</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>14</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>14</v>
+        <v>410</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>24</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>10.85</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>24</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>205</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>14</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>63</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>180</v>
       </c>
     </row>
